--- a/data/controles_results/dif_medias/controls_staggered_vars/difmedias_controles_staggered_variables_2022_T4_0.xlsx
+++ b/data/controles_results/dif_medias/controls_staggered_vars/difmedias_controles_staggered_variables_2022_T4_0.xlsx
@@ -45,7 +45,7 @@
     <t>N</t>
   </si>
   <si>
-    <t>57</t>
+    <t>51</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -63,28 +63,28 @@
     <t>(0.000)</t>
   </si>
   <si>
-    <t>0.491</t>
+    <t>0.549</t>
+  </si>
+  <si>
+    <t>(0.070)</t>
+  </si>
+  <si>
+    <t>0.333</t>
   </si>
   <si>
     <t>(0.067)</t>
   </si>
   <si>
-    <t>0.298</t>
-  </si>
-  <si>
-    <t>(0.061)</t>
-  </si>
-  <si>
-    <t>1.053</t>
-  </si>
-  <si>
-    <t>(0.191)</t>
-  </si>
-  <si>
-    <t>0.386</t>
-  </si>
-  <si>
-    <t>(0.089)</t>
+    <t>1.176</t>
+  </si>
+  <si>
+    <t>(0.207)</t>
+  </si>
+  <si>
+    <t>0.431</t>
+  </si>
+  <si>
+    <t>(0.098)</t>
   </si>
   <si>
     <t>59</t>
@@ -123,7 +123,7 @@
     <t>.n</t>
   </si>
   <si>
-    <t>116</t>
+    <t>110</t>
   </si>
   <si>
     <t>(2)-(1)</t>
@@ -135,16 +135,16 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>0.390***</t>
-  </si>
-  <si>
-    <t>0.329***</t>
-  </si>
-  <si>
-    <t>3.405***</t>
-  </si>
-  <si>
-    <t>1.326***</t>
+    <t>0.332***</t>
+  </si>
+  <si>
+    <t>0.294***</t>
+  </si>
+  <si>
+    <t>3.281***</t>
+  </si>
+  <si>
+    <t>1.280***</t>
   </si>
 </sst>
 </file>
